--- a/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/prdownequitychan/PrdOwnEquityChan.xlsx
+++ b/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/prdownequitychan/PrdOwnEquityChan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20373"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F88799-F027-4ECA-A61F-BA790DEF6675}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B8E5A3-0350-4D7D-9F4B-0E2E4C24173C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>本年累计</t>
   </si>
   <si>
-    <t>#{dtoList.project}</t>
-  </si>
-  <si>
     <t>#{dtoList.thisTermAmt}</t>
   </si>
   <si>
@@ -47,6 +44,10 @@
   </si>
   <si>
     <t>${title}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#{dtoList.subjectName}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -84,6 +85,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -101,6 +103,7 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -108,6 +111,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -115,6 +119,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -800,7 +805,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20.25" x14ac:dyDescent="0.15">
       <c r="A1" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -829,13 +834,13 @@
     </row>
     <row r="4" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
